--- a/astro-site/public/dl/guia-pasteleria-obrador/plantilla-turnos-y-coste-personal.xlsx
+++ b/astro-site/public/dl/guia-pasteleria-obrador/plantilla-turnos-y-coste-personal.xlsx
@@ -3484,7 +3484,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>El pico que decide el año. Referencias de escala, nunca de precio ni de cuota: PS-35 (unos 30 millones de roscones en España en la campaña 2025/26), PS-36 (más de 2,9 millones en la Comunidad de Madrid) y PS-38 (El Corte Inglés 850.000, Viena Capellanes 72.000). PS-46: el supermercado entra con rosc</t>
+          <t>El pico que decide el año. Las unidades de campaña son las de los CINCO días de más venta: 160 al día, 800 en total, el 47 % de los roscones que el mix de la carta asigna al año (1,2 % de las piezas). El resto se venden en la semana previa, fuera de la ventana de campaña, y por eso no entran en esta</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Ocho días seguidos de producción extra, que es más agotador que los cinco de Reyes aunque el pico sea menor. Torrijas y monas a la vez: una necesita freidora y frío, la otra horno y chocolate.</t>
+          <t xml:space="preserve">Ocho días seguidos de producción extra, que es más agotador que los cinco de Reyes aunque el pico sea menor. Torrijas y monas a la vez: una necesita freidora y frío, la otra horno y chocolate. Son 230 torrijas al día y 1.840 en la campaña: el 99 % de las que el mix de la carta asigna al año, porque </t>
         </is>
       </c>
     </row>
